--- a/sources/lei_step6b.xlsx
+++ b/sources/lei_step6b.xlsx
@@ -423,7 +423,7 @@
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -2460,12 +2460,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>f,N+1 [u_d]</t>
+          <t>f,N+1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Razor Rush [SNA]</t>
+          <t>Razor Rush</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>(~U)SNA; (~D)SNA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2522,12 +2527,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>f,N+1&lt;2 [u_d]</t>
+          <t>f,N+1&lt;2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Razor Rush [DGN]</t>
+          <t>Razor Rush</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>(~U)DGN; (~D)DGN</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2584,12 +2594,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>f,N+1&lt;2&lt;1 [u_d]</t>
+          <t>f,N+1&lt;2&lt;1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Razor Rush [PAN]</t>
+          <t>Razor Rush</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>(~U)PAN; (~D)PAN</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2646,12 +2661,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>f,N+1&lt;2&lt;1&lt;2 [u_d]</t>
+          <t>f,N+1&lt;2&lt;1&lt;2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Razor Rush [TGR]</t>
+          <t>Razor Rush</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>(~U)TGR; (~D)TGR</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2765,12 +2785,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>– &lt;4 [u_d]</t>
+          <t>– &lt;4</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>– Crane Kick [CRA]</t>
+          <t>– Crane Kick</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>(~U)CRA; (~D)CRA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3013,12 +3038,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>b+1 [~f]</t>
+          <t>b+1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Drunken Tiger Lash - [DRU]</t>
+          <t>Drunken Tiger Lash</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>(~F)DRU</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3070,12 +3100,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SS+1 [~f] [~d_~u]</t>
+          <t>SS+1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Snake Strike [TGR] [DGN]</t>
+          <t>Snake Strike</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>(~F)TGR; (~D)DGN; (~U)DGN</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3127,12 +3162,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>f+1+2 [~f] [~d_~u]</t>
+          <t>f+1+2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Twin Snake Strikes [CRA] [PAN]</t>
+          <t>Twin Snake Strikes</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>(~F)CRA; (~D)PAN; (~U)PAN</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3392,12 +3432,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>– &lt;4 [u_d]</t>
+          <t>– &lt;4</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>– Crane Kick [CRA]</t>
+          <t>– Crane Kick</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>(~U)CRA; (~D)CRA</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3434,12 +3479,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SS+2,2 [~f]</t>
+          <t>SS+2,2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Drunken Rapid Fists [DRU]</t>
+          <t>Drunken Rapid Fists</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>(~F)DRU</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3558,17 +3608,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3~4 [d]</t>
+          <t>3~4</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tornado Kick [KND]</t>
+          <t>Tornado Kick</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>BT; (~D)KND</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3667,17 +3717,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3~4,U [d]</t>
+          <t>3~4,U</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Triple Tornado [KND]</t>
+          <t>Triple Tornado</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>BT; (~D)KND</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3714,17 +3764,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>f+3~4 [d]</t>
+          <t>f+3~4</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Axis Shift Tornado Kick [KND]</t>
+          <t>Axis Shift Tornado Kick</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>BT; (~D)KND</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3823,17 +3873,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>f+3~4,U [d]</t>
+          <t>f+3~4,U</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Axis Shift Tornado Kick [KND]</t>
+          <t>Axis Shift Tornado Kick</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>BT; (~D)KND</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4673,12 +4723,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>–– &lt;4 [u_d]</t>
+          <t>–– &lt;4</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>–– Crane Kick [CRA]</t>
+          <t>–– Crane Kick</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>(~U)CRA; (~D)CRA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4730,12 +4785,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>db+4 [u_d]</t>
+          <t>db+4</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Rave Sweep [SNA]</t>
+          <t>Rave Sweep</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>(~U)SNA; (~D)SNA</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5401,12 +5461,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>– 1 [~F]</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>– Drunken Tiger Lash [DRU]</t>
+          <t>– Drunken Tiger Lash</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>(~F)DRU</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5463,12 +5528,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>– 2,2 [~F]</t>
+          <t>– 2,2</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>– Drunken Rapid Fists [DRU]</t>
+          <t>– Drunken Rapid Fists</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>(~F)DRU</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6574,17 +6644,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>FC+4 [u_d]</t>
+          <t>FC+4</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>d+4 [u_d]</t>
+          <t>d+4</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Rave Sweep [SNA]</t>
+          <t>Rave Sweep</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>(~U)SNA; (~D)SNA</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7515,12 +7590,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>– 1 [u_d]</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>– Razor Rush [SNA]</t>
+          <t>– Razor Rush</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>(~U)SNA; (~D)SNA</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -7557,12 +7637,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>– 1&lt;2 [u_d]</t>
+          <t>– 1&lt;2</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>– Razor Rush [DGN]</t>
+          <t>– Razor Rush</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>(~U)DGN; (~D)DGN</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -7599,12 +7684,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>– 1&lt;2&lt;1 [u_d]</t>
+          <t>– 1&lt;2&lt;1</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>– Razor Rush [PAN]</t>
+          <t>– Razor Rush</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>(~U)PAN; (~D)PAN</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -7641,12 +7731,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>– 1&lt;2&lt;1&lt;2 [u_d]</t>
+          <t>– 1&lt;2&lt;1&lt;2</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>– Razor Rush [TGR]</t>
+          <t>– Razor Rush</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>(~U)TGR; (~D)TGR</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -7755,12 +7850,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>–– &lt;4 [u_d]</t>
+          <t>–– &lt;4</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>–– Crane Kick [CRA]</t>
+          <t>–– Crane Kick</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>(~U)CRA; (~D)CRA</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -8477,12 +8577,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>3 [~B]</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Panther Tail [Art of Phoenix]</t>
+          <t>Panther Tail</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>(~B)AOP</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -8710,12 +8815,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>–– &lt;4 [u_d]</t>
+          <t>–– &lt;4</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>–– Crane Kick [CRA]</t>
+          <t>–– Crane Kick</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>(~U)CRA; (~D)CRA</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -8961,12 +9071,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1+2 [~F]</t>
+          <t>1+2</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Dragon Spark - [TGR]</t>
+          <t>Dragon Spark</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>(~F)TGR</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9023,12 +9138,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2 [~F]</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Dragon Roar - [TGR]</t>
+          <t>Dragon Roar</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>(~F)TGR</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9522,12 +9642,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1~1~1~1~1~1 [~F]</t>
+          <t>1~1~1~1~1~1</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Rushing Snake [SNA]</t>
+          <t>Rushing Snake</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>(~F)SNA</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -9584,12 +9709,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2 [~F]</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Single Snake Bite [DGN]</t>
+          <t>Single Snake Bite</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>(~F)DGN</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -9646,12 +9776,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2,2 [~F]</t>
+          <t>2,2</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Double Snake Bite [DGN]</t>
+          <t>Double Snake Bite</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>(~F)DGN</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -9854,12 +9989,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2,2,2 [~F]</t>
+          <t>2,2,2</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Triple Snake Bite [PAN]</t>
+          <t>Triple Snake Bite</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>(~F)PAN</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -10530,17 +10670,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>b+4 [d]</t>
+          <t>b+4</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Tornado Kick [KND]</t>
+          <t>Tornado Kick</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>BT; (~D)KND</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -10572,17 +10712,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>b+4,U [d]</t>
+          <t>b+4,U</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Triple Tornado [KND]</t>
+          <t>Triple Tornado</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>BT; (~D)KND</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">

--- a/sources/lei_step6b.xlsx
+++ b/sources/lei_step6b.xlsx
@@ -832,6 +832,11 @@
           <t>Lei regains 10 points of energy but the throw damage is reduced to 23.</t>
         </is>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>915f6ce4-1f16-4f29-88a0-289bf4714220</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
           <t>915f6ce4-1f16-4f29-88a0-289bf4714220</t>
@@ -884,6 +889,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1fb94b7c-cb38-4d16-8f0b-b543560350e1</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>1fb94b7c-cb38-4d16-8f0b-b543560350e1</t>
@@ -931,6 +941,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>ffe412b1-5618-4c64-9fba-93d447318548</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
           <t>ffe412b1-5618-4c64-9fba-93d447318548</t>
@@ -976,6 +991,11 @@
       <c r="M11" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>3376e300-d34c-4e03-990c-8cf3dac1403a</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -10487,6 +10507,11 @@
           <t>hhlMmmhmmh</t>
         </is>
       </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>3b08195b-3ba2-4ba2-b20d-f82f3f97efcc</t>
+        </is>
+      </c>
       <c r="R193" t="inlineStr">
         <is>
           <t>3b08195b-3ba2-4ba2-b20d-f82f3f97efcc</t>
@@ -10514,6 +10539,11 @@
           <t>hhlMmmhmLh</t>
         </is>
       </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>ad8ba5a0-00eb-4959-9a6d-1b52886c113e</t>
+        </is>
+      </c>
       <c r="R194" t="inlineStr">
         <is>
           <t>ad8ba5a0-00eb-4959-9a6d-1b52886c113e</t>
@@ -10544,6 +10574,11 @@
       <c r="P195" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>1e9286e9-8453-4085-abd5-d467b2a34a10</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
